--- a/complete/FINAL_NYAHURURU_LOANS.xlsx
+++ b/complete/FINAL_NYAHURURU_LOANS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\KashLeo data\complete\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECB79AA1-5875-4AB8-8408-B5E3CF5A1A29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC80C510-7EC8-4125-9EF8-CFD954A9DCA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="10170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1302" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1286" uniqueCount="373">
   <si>
     <t>Disbursement Date</t>
   </si>
@@ -394,22 +394,10 @@
     <t>6/10/2026 0:00</t>
   </si>
   <si>
-    <t>Daniel Wambui</t>
-  </si>
-  <si>
-    <t>Sabina Akope</t>
-  </si>
-  <si>
     <t>Jecinta Nduta</t>
   </si>
   <si>
     <t xml:space="preserve">Grace Njuguna </t>
-  </si>
-  <si>
-    <t>Fatuma Duba</t>
-  </si>
-  <si>
-    <t>Stephen Kipkurui</t>
   </si>
   <si>
     <t>September</t>
@@ -3900,71 +3888,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A42" t="s">
-        <v>123</v>
-      </c>
-      <c r="B42" t="s">
-        <v>124</v>
-      </c>
-      <c r="C42">
-        <v>728981668</v>
-      </c>
-      <c r="D42">
-        <v>21198347</v>
-      </c>
-      <c r="E42" t="s">
-        <v>125</v>
-      </c>
-      <c r="F42">
-        <v>769325233</v>
-      </c>
-      <c r="G42">
-        <v>32435433</v>
-      </c>
-      <c r="H42">
-        <v>7000</v>
-      </c>
-      <c r="I42" t="s">
-        <v>29</v>
-      </c>
-      <c r="J42">
-        <v>500</v>
-      </c>
-      <c r="K42">
-        <v>3000</v>
-      </c>
-      <c r="L42">
-        <v>10000</v>
-      </c>
-      <c r="M42">
-        <v>1667</v>
-      </c>
-      <c r="N42">
-        <v>0</v>
-      </c>
-      <c r="O42">
-        <v>10000</v>
-      </c>
-      <c r="P42" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q42" t="s">
-        <v>24</v>
-      </c>
-      <c r="R42" t="s">
-        <v>87</v>
-      </c>
-      <c r="S42" t="s">
-        <v>30</v>
-      </c>
-    </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>123</v>
       </c>
       <c r="B43" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C43">
         <v>769621536</v>
@@ -3973,7 +3902,7 @@
         <v>13668008</v>
       </c>
       <c r="E43" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F43">
         <v>724544938</v>
@@ -4018,79 +3947,20 @@
         <v>30</v>
       </c>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A44" t="s">
-        <v>123</v>
-      </c>
-      <c r="B44" t="s">
-        <v>128</v>
-      </c>
-      <c r="C44">
-        <v>116140156</v>
-      </c>
-      <c r="D44">
-        <v>27198409</v>
-      </c>
-      <c r="E44" t="s">
-        <v>129</v>
-      </c>
-      <c r="F44">
-        <v>798372422</v>
-      </c>
-      <c r="G44">
-        <v>39235403</v>
-      </c>
-      <c r="H44">
-        <v>17000</v>
-      </c>
-      <c r="I44" t="s">
-        <v>29</v>
-      </c>
-      <c r="J44">
-        <v>1190</v>
-      </c>
-      <c r="K44">
-        <v>5100</v>
-      </c>
-      <c r="L44">
-        <v>22100</v>
-      </c>
-      <c r="M44">
-        <v>3684</v>
-      </c>
-      <c r="N44">
-        <v>0</v>
-      </c>
-      <c r="O44">
-        <v>22100</v>
-      </c>
-      <c r="P44" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q44" t="s">
-        <v>24</v>
-      </c>
-      <c r="R44" t="s">
-        <v>87</v>
-      </c>
-      <c r="S44" t="s">
-        <v>99</v>
-      </c>
-    </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.35">
       <c r="Q45" t="s">
         <v>24</v>
       </c>
       <c r="R45" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B46" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C46">
         <v>711686002</v>
@@ -4099,7 +3969,7 @@
         <v>13844502</v>
       </c>
       <c r="E46" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="F46">
         <v>757069418</v>
@@ -4138,7 +4008,7 @@
         <v>24</v>
       </c>
       <c r="R46" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S46" t="s">
         <v>69</v>
@@ -4146,10 +4016,10 @@
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B47" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C47">
         <v>714716360</v>
@@ -4158,7 +4028,7 @@
         <v>33092811</v>
       </c>
       <c r="E47" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F47">
         <v>758589148</v>
@@ -4197,7 +4067,7 @@
         <v>24</v>
       </c>
       <c r="R47" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S47" t="s">
         <v>30</v>
@@ -4205,10 +4075,10 @@
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B48" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C48">
         <v>705304253</v>
@@ -4217,7 +4087,7 @@
         <v>28687504</v>
       </c>
       <c r="E48" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="F48">
         <v>706841567</v>
@@ -4256,7 +4126,7 @@
         <v>24</v>
       </c>
       <c r="R48" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S48" t="s">
         <v>30</v>
@@ -4264,10 +4134,10 @@
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B49" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C49">
         <v>113300495</v>
@@ -4276,7 +4146,7 @@
         <v>20606674</v>
       </c>
       <c r="E49" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="F49">
         <v>721920114</v>
@@ -4312,7 +4182,7 @@
         <v>24</v>
       </c>
       <c r="R49" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S49" t="s">
         <v>30</v>
@@ -4320,10 +4190,10 @@
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B50" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C50">
         <v>725709459</v>
@@ -4332,7 +4202,7 @@
         <v>4356631</v>
       </c>
       <c r="E50" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F50">
         <v>722416830</v>
@@ -4371,7 +4241,7 @@
         <v>24</v>
       </c>
       <c r="R50" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S50" t="s">
         <v>30</v>
@@ -4379,10 +4249,10 @@
     </row>
     <row r="51" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B51" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C51">
         <v>714885607</v>
@@ -4430,7 +4300,7 @@
         <v>24</v>
       </c>
       <c r="R51" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S51" t="s">
         <v>69</v>
@@ -4438,10 +4308,10 @@
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B52" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C52">
         <v>710540080</v>
@@ -4450,7 +4320,7 @@
         <v>22039462</v>
       </c>
       <c r="E52" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="F52">
         <v>724066021</v>
@@ -4489,7 +4359,7 @@
         <v>24</v>
       </c>
       <c r="R52" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S52" t="s">
         <v>69</v>
@@ -4497,10 +4367,10 @@
     </row>
     <row r="53" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B53" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C53">
         <v>746828913</v>
@@ -4509,7 +4379,7 @@
         <v>37703695</v>
       </c>
       <c r="E53" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F53">
         <v>718529941</v>
@@ -4545,7 +4415,7 @@
         <v>24</v>
       </c>
       <c r="R53" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S53" t="s">
         <v>30</v>
@@ -4553,10 +4423,10 @@
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="B54" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="C54">
         <v>796216948</v>
@@ -4565,7 +4435,7 @@
         <v>7665674</v>
       </c>
       <c r="E54" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F54">
         <v>720001026</v>
@@ -4604,7 +4474,7 @@
         <v>24</v>
       </c>
       <c r="R54" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S54" t="s">
         <v>30</v>
@@ -4612,10 +4482,10 @@
     </row>
     <row r="55" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B55" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C55">
         <v>742982500</v>
@@ -4624,7 +4494,7 @@
         <v>2620781</v>
       </c>
       <c r="E55" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="F55">
         <v>723791251</v>
@@ -4663,7 +4533,7 @@
         <v>24</v>
       </c>
       <c r="R55" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S55" t="s">
         <v>30</v>
@@ -4671,10 +4541,10 @@
     </row>
     <row r="56" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B56" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C56">
         <v>7922579608</v>
@@ -4683,7 +4553,7 @@
         <v>34260988</v>
       </c>
       <c r="E56" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="F56">
         <v>743748162</v>
@@ -4722,7 +4592,7 @@
         <v>24</v>
       </c>
       <c r="R56" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S56" t="s">
         <v>30</v>
@@ -4730,10 +4600,10 @@
     </row>
     <row r="57" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B57" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C57">
         <v>724446422</v>
@@ -4742,7 +4612,7 @@
         <v>8620840</v>
       </c>
       <c r="E57" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="F57">
         <v>726768133</v>
@@ -4781,7 +4651,7 @@
         <v>24</v>
       </c>
       <c r="R57" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S57" t="s">
         <v>30</v>
@@ -4789,10 +4659,10 @@
     </row>
     <row r="58" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B58" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="C58">
         <v>746405759</v>
@@ -4801,7 +4671,7 @@
         <v>20640527</v>
       </c>
       <c r="E58" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="F58">
         <v>718102970</v>
@@ -4840,7 +4710,7 @@
         <v>24</v>
       </c>
       <c r="R58" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S58" t="s">
         <v>30</v>
@@ -4848,10 +4718,10 @@
     </row>
     <row r="59" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B59" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="C59">
         <v>799871943</v>
@@ -4860,7 +4730,7 @@
         <v>13395242</v>
       </c>
       <c r="E59" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="F59">
         <v>742728359</v>
@@ -4899,7 +4769,7 @@
         <v>24</v>
       </c>
       <c r="R59" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S59" t="s">
         <v>69</v>
@@ -4907,10 +4777,10 @@
     </row>
     <row r="60" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B60" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C60">
         <v>706439225</v>
@@ -4919,7 +4789,7 @@
         <v>22580679</v>
       </c>
       <c r="E60" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F60">
         <v>10660229</v>
@@ -4958,7 +4828,7 @@
         <v>24</v>
       </c>
       <c r="R60" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S60" t="s">
         <v>88</v>
@@ -4966,10 +4836,10 @@
     </row>
     <row r="61" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B61" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C61">
         <v>721111140</v>
@@ -4978,13 +4848,13 @@
         <v>25332821</v>
       </c>
       <c r="E61" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="F61">
         <v>712561516</v>
       </c>
       <c r="G61" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="H61">
         <v>7000</v>
@@ -5017,7 +4887,7 @@
         <v>24</v>
       </c>
       <c r="R61" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S61" t="s">
         <v>30</v>
@@ -5025,10 +4895,10 @@
     </row>
     <row r="62" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B62" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="C62">
         <v>797064363</v>
@@ -5037,7 +4907,7 @@
         <v>29299181</v>
       </c>
       <c r="E62" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="F62">
         <v>717892112</v>
@@ -5076,7 +4946,7 @@
         <v>24</v>
       </c>
       <c r="R62" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S62" t="s">
         <v>30</v>
@@ -5084,10 +4954,10 @@
     </row>
     <row r="63" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B63" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="C63">
         <v>715706681</v>
@@ -5096,7 +4966,7 @@
         <v>28779840</v>
       </c>
       <c r="E63" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="F63">
         <v>722948117</v>
@@ -5135,18 +5005,18 @@
         <v>24</v>
       </c>
       <c r="R63" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S63" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="64" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
+        <v>164</v>
+      </c>
+      <c r="B64" t="s">
         <v>168</v>
-      </c>
-      <c r="B64" t="s">
-        <v>172</v>
       </c>
       <c r="C64">
         <v>723495587</v>
@@ -5155,7 +5025,7 @@
         <v>23411441</v>
       </c>
       <c r="E64" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="F64">
         <v>729417206</v>
@@ -5194,7 +5064,7 @@
         <v>24</v>
       </c>
       <c r="R64" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S64" t="s">
         <v>69</v>
@@ -5202,10 +5072,10 @@
     </row>
     <row r="65" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B65" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C65">
         <v>704424647</v>
@@ -5214,7 +5084,7 @@
         <v>20252308</v>
       </c>
       <c r="E65" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="F65">
         <v>711767396</v>
@@ -5253,7 +5123,7 @@
         <v>24</v>
       </c>
       <c r="R65" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S65" t="s">
         <v>30</v>
@@ -5261,10 +5131,10 @@
     </row>
     <row r="66" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B66" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C66">
         <v>700480519</v>
@@ -5273,7 +5143,7 @@
         <v>23593717</v>
       </c>
       <c r="E66" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="F66">
         <v>715873084</v>
@@ -5312,7 +5182,7 @@
         <v>24</v>
       </c>
       <c r="R66" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S66" t="s">
         <v>30</v>
@@ -5320,10 +5190,10 @@
     </row>
     <row r="67" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="B67" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="C67">
         <v>712833328</v>
@@ -5332,7 +5202,7 @@
         <v>11707589</v>
       </c>
       <c r="E67" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="F67">
         <v>792402413</v>
@@ -5371,7 +5241,7 @@
         <v>24</v>
       </c>
       <c r="R67" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S67" t="s">
         <v>69</v>
@@ -5379,10 +5249,10 @@
     </row>
     <row r="68" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="B68" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C68">
         <v>715365131</v>
@@ -5391,7 +5261,7 @@
         <v>10119342</v>
       </c>
       <c r="E68" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="F68">
         <v>713543764</v>
@@ -5430,7 +5300,7 @@
         <v>24</v>
       </c>
       <c r="R68" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S68" t="s">
         <v>69</v>
@@ -5438,10 +5308,10 @@
     </row>
     <row r="69" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="B69" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C69">
         <v>702028822</v>
@@ -5450,7 +5320,7 @@
         <v>8207591</v>
       </c>
       <c r="E69" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F69">
         <v>713501528</v>
@@ -5489,7 +5359,7 @@
         <v>24</v>
       </c>
       <c r="R69" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S69" t="s">
         <v>30</v>
@@ -5497,10 +5367,10 @@
     </row>
     <row r="70" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="B70" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C70">
         <v>758394044</v>
@@ -5509,7 +5379,7 @@
         <v>40455673</v>
       </c>
       <c r="E70" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F70">
         <v>746652412</v>
@@ -5548,7 +5418,7 @@
         <v>24</v>
       </c>
       <c r="R70" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S70" t="s">
         <v>30</v>
@@ -5556,10 +5426,10 @@
     </row>
     <row r="71" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="B71" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C71">
         <v>708448209</v>
@@ -5568,7 +5438,7 @@
         <v>614340</v>
       </c>
       <c r="E71" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F71">
         <v>116691166</v>
@@ -5607,7 +5477,7 @@
         <v>24</v>
       </c>
       <c r="R71" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S71" t="s">
         <v>30</v>
@@ -5615,10 +5485,10 @@
     </row>
     <row r="72" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="B72" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C72">
         <v>703915750</v>
@@ -5627,7 +5497,7 @@
         <v>6091456</v>
       </c>
       <c r="E72" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F72">
         <v>720024027</v>
@@ -5666,7 +5536,7 @@
         <v>24</v>
       </c>
       <c r="R72" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S72" t="s">
         <v>30</v>
@@ -5674,10 +5544,10 @@
     </row>
     <row r="73" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="B73" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C73">
         <v>757091865</v>
@@ -5686,7 +5556,7 @@
         <v>31280903</v>
       </c>
       <c r="E73" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="F73">
         <v>725084524</v>
@@ -5725,7 +5595,7 @@
         <v>24</v>
       </c>
       <c r="R73" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S73" t="s">
         <v>30</v>
@@ -5733,10 +5603,10 @@
     </row>
     <row r="74" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B74" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C74">
         <v>727387416</v>
@@ -5745,7 +5615,7 @@
         <v>9056128</v>
       </c>
       <c r="E74" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="F74">
         <v>710954164</v>
@@ -5784,7 +5654,7 @@
         <v>24</v>
       </c>
       <c r="R74" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S74" t="s">
         <v>30</v>
@@ -5792,10 +5662,10 @@
     </row>
     <row r="75" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B75" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C75">
         <v>727865456</v>
@@ -5804,7 +5674,7 @@
         <v>10892446</v>
       </c>
       <c r="E75" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="F75">
         <v>726503829</v>
@@ -5843,7 +5713,7 @@
         <v>24</v>
       </c>
       <c r="R75" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S75" t="s">
         <v>81</v>
@@ -5851,10 +5721,10 @@
     </row>
     <row r="76" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B76" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="C76">
         <v>741590773</v>
@@ -5863,7 +5733,7 @@
         <v>23494763</v>
       </c>
       <c r="E76" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="F76">
         <v>791282933</v>
@@ -5902,7 +5772,7 @@
         <v>24</v>
       </c>
       <c r="R76" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S76" t="s">
         <v>30</v>
@@ -5910,10 +5780,10 @@
     </row>
     <row r="77" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B77" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C77">
         <v>795544079</v>
@@ -5922,7 +5792,7 @@
         <v>35917647</v>
       </c>
       <c r="E77" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="F77">
         <v>713472309</v>
@@ -5961,7 +5831,7 @@
         <v>24</v>
       </c>
       <c r="R77" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S77" t="s">
         <v>30</v>
@@ -5969,10 +5839,10 @@
     </row>
     <row r="78" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B78" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="C78">
         <v>721994091</v>
@@ -5981,7 +5851,7 @@
         <v>1032563</v>
       </c>
       <c r="E78" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F78">
         <v>715747740</v>
@@ -6020,7 +5890,7 @@
         <v>24</v>
       </c>
       <c r="R78" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S78" t="s">
         <v>30</v>
@@ -6028,10 +5898,10 @@
     </row>
     <row r="79" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B79" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="C79">
         <v>795157747</v>
@@ -6040,7 +5910,7 @@
         <v>3723880</v>
       </c>
       <c r="E79" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="F79">
         <v>757630138</v>
@@ -6079,7 +5949,7 @@
         <v>24</v>
       </c>
       <c r="R79" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S79" t="s">
         <v>30</v>
@@ -6087,10 +5957,10 @@
     </row>
     <row r="80" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B80" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C80">
         <v>720552419</v>
@@ -6099,7 +5969,7 @@
         <v>871989</v>
       </c>
       <c r="E80" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="F80">
         <v>756240295</v>
@@ -6138,7 +6008,7 @@
         <v>24</v>
       </c>
       <c r="R80" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S80" t="s">
         <v>30</v>
@@ -6146,10 +6016,10 @@
     </row>
     <row r="81" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B81" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C81">
         <v>706607577</v>
@@ -6158,7 +6028,7 @@
         <v>5173672</v>
       </c>
       <c r="E81" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="F81">
         <v>743458451</v>
@@ -6197,7 +6067,7 @@
         <v>24</v>
       </c>
       <c r="R81" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S81" t="s">
         <v>30</v>
@@ -6205,10 +6075,10 @@
     </row>
     <row r="82" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B82" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="C82">
         <v>112149690</v>
@@ -6217,7 +6087,7 @@
         <v>21334655</v>
       </c>
       <c r="E82" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="F82">
         <v>759900772</v>
@@ -6256,7 +6126,7 @@
         <v>24</v>
       </c>
       <c r="R82" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S82" t="s">
         <v>99</v>
@@ -6264,10 +6134,10 @@
     </row>
     <row r="83" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B83" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="C83">
         <v>707593937</v>
@@ -6276,7 +6146,7 @@
         <v>10512633</v>
       </c>
       <c r="E83" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="F83">
         <v>704452061</v>
@@ -6315,7 +6185,7 @@
         <v>24</v>
       </c>
       <c r="R83" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S83" t="s">
         <v>30</v>
@@ -6323,10 +6193,10 @@
     </row>
     <row r="84" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B84" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="C84">
         <v>724164082</v>
@@ -6335,7 +6205,7 @@
         <v>10316527</v>
       </c>
       <c r="E84" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="F84">
         <v>727992553</v>
@@ -6374,7 +6244,7 @@
         <v>24</v>
       </c>
       <c r="R84" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S84" t="s">
         <v>88</v>
@@ -6382,10 +6252,10 @@
     </row>
     <row r="85" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B85" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C85">
         <v>715228494</v>
@@ -6394,7 +6264,7 @@
         <v>30049769</v>
       </c>
       <c r="E85" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="F85">
         <v>727816849</v>
@@ -6433,7 +6303,7 @@
         <v>24</v>
       </c>
       <c r="R85" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S85" t="s">
         <v>30</v>
@@ -6441,10 +6311,10 @@
     </row>
     <row r="86" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="B86" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C86">
         <v>799332321</v>
@@ -6453,7 +6323,7 @@
         <v>213687386</v>
       </c>
       <c r="E86" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="F86">
         <v>717004382</v>
@@ -6492,7 +6362,7 @@
         <v>24</v>
       </c>
       <c r="R86" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S86" t="s">
         <v>30</v>
@@ -6500,10 +6370,10 @@
     </row>
     <row r="87" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="B87" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C87">
         <v>701169467</v>
@@ -6512,7 +6382,7 @@
         <v>24095273</v>
       </c>
       <c r="E87" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="F87">
         <v>712438585</v>
@@ -6551,7 +6421,7 @@
         <v>24</v>
       </c>
       <c r="R87" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S87" t="s">
         <v>30</v>
@@ -6559,10 +6429,10 @@
     </row>
     <row r="88" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="B88" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="C88">
         <v>718846710</v>
@@ -6571,7 +6441,7 @@
         <v>13068688</v>
       </c>
       <c r="E88" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="F88">
         <v>708382465</v>
@@ -6610,7 +6480,7 @@
         <v>24</v>
       </c>
       <c r="R88" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S88" t="s">
         <v>69</v>
@@ -6618,10 +6488,10 @@
     </row>
     <row r="89" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="B89" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C89">
         <v>797775990</v>
@@ -6630,7 +6500,7 @@
         <v>8077101</v>
       </c>
       <c r="E89" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F89">
         <v>748608288</v>
@@ -6669,7 +6539,7 @@
         <v>24</v>
       </c>
       <c r="R89" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S89" t="s">
         <v>69</v>
@@ -6677,10 +6547,10 @@
     </row>
     <row r="90" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="B90" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C90">
         <v>718871498</v>
@@ -6689,7 +6559,7 @@
         <v>24134466</v>
       </c>
       <c r="E90" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="F90">
         <v>700144012</v>
@@ -6728,7 +6598,7 @@
         <v>24</v>
       </c>
       <c r="R90" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S90" t="s">
         <v>30</v>
@@ -6736,10 +6606,10 @@
     </row>
     <row r="91" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="B91" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C91">
         <v>727877025</v>
@@ -6748,7 +6618,7 @@
         <v>27653272</v>
       </c>
       <c r="E91" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="F91">
         <v>726297808</v>
@@ -6787,7 +6657,7 @@
         <v>24</v>
       </c>
       <c r="R91" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S91" t="s">
         <v>30</v>
@@ -6795,10 +6665,10 @@
     </row>
     <row r="92" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="B92" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="C92">
         <v>759900772</v>
@@ -6807,7 +6677,7 @@
         <v>39410076</v>
       </c>
       <c r="E92" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="F92">
         <v>710625385</v>
@@ -6846,7 +6716,7 @@
         <v>24</v>
       </c>
       <c r="R92" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S92" t="s">
         <v>88</v>
@@ -6854,10 +6724,10 @@
     </row>
     <row r="93" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="B93" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="C93">
         <v>727364504</v>
@@ -6866,7 +6736,7 @@
         <v>27206497</v>
       </c>
       <c r="E93" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="F93">
         <v>792519004</v>
@@ -6905,7 +6775,7 @@
         <v>24</v>
       </c>
       <c r="R93" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S93" t="s">
         <v>69</v>
@@ -6913,10 +6783,10 @@
     </row>
     <row r="94" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="B94" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C94">
         <v>794416300</v>
@@ -6925,7 +6795,7 @@
         <v>7436666</v>
       </c>
       <c r="E94" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="F94">
         <v>728397868</v>
@@ -6964,7 +6834,7 @@
         <v>24</v>
       </c>
       <c r="R94" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S94" t="s">
         <v>30</v>
@@ -6972,10 +6842,10 @@
     </row>
     <row r="95" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="B95" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="C95">
         <v>729417206</v>
@@ -6984,7 +6854,7 @@
         <v>8678387</v>
       </c>
       <c r="E95" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="F95">
         <v>745945541</v>
@@ -7023,7 +6893,7 @@
         <v>24</v>
       </c>
       <c r="R95" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S95" t="s">
         <v>30</v>
@@ -7031,10 +6901,10 @@
     </row>
     <row r="96" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
+        <v>234</v>
+      </c>
+      <c r="B96" t="s">
         <v>238</v>
-      </c>
-      <c r="B96" t="s">
-        <v>242</v>
       </c>
       <c r="C96">
         <v>705400456</v>
@@ -7043,7 +6913,7 @@
         <v>14476495</v>
       </c>
       <c r="E96" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="F96">
         <v>746322882</v>
@@ -7082,7 +6952,7 @@
         <v>24</v>
       </c>
       <c r="R96" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S96" t="s">
         <v>30</v>
@@ -7090,10 +6960,10 @@
     </row>
     <row r="97" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="B97" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="C97">
         <v>720340478</v>
@@ -7102,7 +6972,7 @@
         <v>23255554</v>
       </c>
       <c r="E97" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="F97">
         <v>720132021</v>
@@ -7114,7 +6984,7 @@
         <v>7000</v>
       </c>
       <c r="I97" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="J97">
         <v>700</v>
@@ -7141,7 +7011,7 @@
         <v>24</v>
       </c>
       <c r="R97" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S97" t="s">
         <v>88</v>
@@ -7149,10 +7019,10 @@
     </row>
     <row r="98" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="B98" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="C98">
         <v>799835033</v>
@@ -7161,7 +7031,7 @@
         <v>28269341</v>
       </c>
       <c r="E98" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="F98">
         <v>726683825</v>
@@ -7200,7 +7070,7 @@
         <v>24</v>
       </c>
       <c r="R98" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S98" t="s">
         <v>30</v>
@@ -7208,10 +7078,10 @@
     </row>
     <row r="99" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="B99" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="C99">
         <v>746811444</v>
@@ -7220,7 +7090,7 @@
         <v>7038285</v>
       </c>
       <c r="E99" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="F99">
         <v>115403692</v>
@@ -7259,7 +7129,7 @@
         <v>24</v>
       </c>
       <c r="R99" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S99" t="s">
         <v>30</v>
@@ -7267,10 +7137,10 @@
     </row>
     <row r="100" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
+        <v>243</v>
+      </c>
+      <c r="B100" t="s">
         <v>247</v>
-      </c>
-      <c r="B100" t="s">
-        <v>251</v>
       </c>
       <c r="C100">
         <v>715390575</v>
@@ -7279,7 +7149,7 @@
         <v>7038431</v>
       </c>
       <c r="E100" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="F100">
         <v>759859581</v>
@@ -7318,7 +7188,7 @@
         <v>24</v>
       </c>
       <c r="R100" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S100" t="s">
         <v>30</v>
@@ -7326,10 +7196,10 @@
     </row>
     <row r="101" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="B101" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="C101">
         <v>724210636</v>
@@ -7338,7 +7208,7 @@
         <v>1392706</v>
       </c>
       <c r="E101" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="F101">
         <v>740491220</v>
@@ -7377,7 +7247,7 @@
         <v>24</v>
       </c>
       <c r="R101" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S101" t="s">
         <v>30</v>
@@ -7385,10 +7255,10 @@
     </row>
     <row r="102" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="B102" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="C102">
         <v>715616331</v>
@@ -7397,7 +7267,7 @@
         <v>36728923</v>
       </c>
       <c r="E102" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F102">
         <v>704690718</v>
@@ -7436,7 +7306,7 @@
         <v>24</v>
       </c>
       <c r="R102" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S102" t="s">
         <v>69</v>
@@ -7444,16 +7314,16 @@
     </row>
     <row r="103" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="B103" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C103">
         <v>740300218</v>
       </c>
       <c r="E103" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="F103">
         <v>722117246</v>
@@ -7492,7 +7362,7 @@
         <v>24</v>
       </c>
       <c r="R103" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S103" t="s">
         <v>30</v>
@@ -7500,10 +7370,10 @@
     </row>
     <row r="104" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="B104" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C104">
         <v>742751846</v>
@@ -7512,7 +7382,7 @@
         <v>39662989</v>
       </c>
       <c r="E104" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="F104">
         <v>750608040</v>
@@ -7551,7 +7421,7 @@
         <v>24</v>
       </c>
       <c r="R104" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S104" t="s">
         <v>30</v>
@@ -7559,10 +7429,10 @@
     </row>
     <row r="105" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="B105" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C105">
         <v>719105265</v>
@@ -7571,7 +7441,7 @@
         <v>11306416</v>
       </c>
       <c r="E105" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="F105">
         <v>726580019</v>
@@ -7610,7 +7480,7 @@
         <v>24</v>
       </c>
       <c r="R105" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S105" t="s">
         <v>30</v>
@@ -7618,10 +7488,10 @@
     </row>
     <row r="106" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="B106" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="C106">
         <v>740605836</v>
@@ -7630,7 +7500,7 @@
         <v>36868661</v>
       </c>
       <c r="E106" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="F106">
         <v>703215864</v>
@@ -7669,7 +7539,7 @@
         <v>24</v>
       </c>
       <c r="R106" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S106" t="s">
         <v>30</v>
@@ -7677,10 +7547,10 @@
     </row>
     <row r="107" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="B107" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="C107">
         <v>792149332</v>
@@ -7728,7 +7598,7 @@
         <v>24</v>
       </c>
       <c r="R107" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S107" t="s">
         <v>30</v>
@@ -7736,10 +7606,10 @@
     </row>
     <row r="108" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="B108" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="C108">
         <v>705102985</v>
@@ -7748,7 +7618,7 @@
         <v>27791326</v>
       </c>
       <c r="E108" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="F108">
         <v>714203055</v>
@@ -7787,7 +7657,7 @@
         <v>24</v>
       </c>
       <c r="R108" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S108" t="s">
         <v>30</v>
@@ -7795,10 +7665,10 @@
     </row>
     <row r="109" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
+        <v>259</v>
+      </c>
+      <c r="B109" t="s">
         <v>263</v>
-      </c>
-      <c r="B109" t="s">
-        <v>267</v>
       </c>
       <c r="C109">
         <v>794029149</v>
@@ -7807,7 +7677,7 @@
         <v>26365817</v>
       </c>
       <c r="E109" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="F109">
         <v>717512042</v>
@@ -7846,7 +7716,7 @@
         <v>24</v>
       </c>
       <c r="R109" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S109" t="s">
         <v>30</v>
@@ -7854,10 +7724,10 @@
     </row>
     <row r="110" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="B110" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="C110">
         <v>796250750</v>
@@ -7866,7 +7736,7 @@
         <v>2944535</v>
       </c>
       <c r="E110" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="F110">
         <v>741199155</v>
@@ -7905,7 +7775,7 @@
         <v>24</v>
       </c>
       <c r="R110" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S110" t="s">
         <v>112</v>
@@ -7913,10 +7783,10 @@
     </row>
     <row r="111" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="B111" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="C111">
         <v>724350985</v>
@@ -7925,7 +7795,7 @@
         <v>24061793</v>
       </c>
       <c r="E111" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="F111">
         <v>796102762</v>
@@ -7964,7 +7834,7 @@
         <v>24</v>
       </c>
       <c r="R111" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S111" t="s">
         <v>88</v>
@@ -7972,10 +7842,10 @@
     </row>
     <row r="112" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="B112" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="C112">
         <v>792612031</v>
@@ -8023,7 +7893,7 @@
         <v>24</v>
       </c>
       <c r="R112" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S112" t="s">
         <v>30</v>
@@ -8031,10 +7901,10 @@
     </row>
     <row r="113" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="B113" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="C113">
         <v>725380367</v>
@@ -8043,7 +7913,7 @@
         <v>7440363</v>
       </c>
       <c r="E113" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="F113">
         <v>728534959</v>
@@ -8082,7 +7952,7 @@
         <v>24</v>
       </c>
       <c r="R113" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S113" t="s">
         <v>30</v>
@@ -8090,10 +7960,10 @@
     </row>
     <row r="114" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="B114" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="C114">
         <v>704244146</v>
@@ -8102,7 +7972,7 @@
         <v>25716147</v>
       </c>
       <c r="E114" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="F114">
         <v>725385232</v>
@@ -8141,7 +8011,7 @@
         <v>24</v>
       </c>
       <c r="R114" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S114" t="s">
         <v>30</v>
@@ -8149,10 +8019,10 @@
     </row>
     <row r="115" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="B115" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="C115">
         <v>714076538</v>
@@ -8161,7 +8031,7 @@
         <v>20957763</v>
       </c>
       <c r="E115" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="F115">
         <v>798654955</v>
@@ -8200,7 +8070,7 @@
         <v>24</v>
       </c>
       <c r="R115" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S115" t="s">
         <v>88</v>
@@ -8208,10 +8078,10 @@
     </row>
     <row r="116" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="B116" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="C116">
         <v>727828552</v>
@@ -8259,7 +8129,7 @@
         <v>24</v>
       </c>
       <c r="R116" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S116" t="s">
         <v>30</v>
@@ -8267,10 +8137,10 @@
     </row>
     <row r="117" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="B117" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="C117">
         <v>725995376</v>
@@ -8279,7 +8149,7 @@
         <v>26558864</v>
       </c>
       <c r="E117" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="F117">
         <v>741508090</v>
@@ -8318,7 +8188,7 @@
         <v>24</v>
       </c>
       <c r="R117" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S117" t="s">
         <v>88</v>
@@ -8326,10 +8196,10 @@
     </row>
     <row r="118" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="B118" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="C118">
         <v>721318231</v>
@@ -8338,7 +8208,7 @@
         <v>22136772</v>
       </c>
       <c r="E118" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="F118">
         <v>705850703</v>
@@ -8377,7 +8247,7 @@
         <v>24</v>
       </c>
       <c r="R118" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S118" t="s">
         <v>69</v>
@@ -8385,10 +8255,10 @@
     </row>
     <row r="119" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="B119" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="C119">
         <v>705191158</v>
@@ -8397,7 +8267,7 @@
         <v>304074763</v>
       </c>
       <c r="E119" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="F119">
         <v>762070095</v>
@@ -8436,7 +8306,7 @@
         <v>24</v>
       </c>
       <c r="R119" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S119" t="s">
         <v>30</v>
@@ -8444,10 +8314,10 @@
     </row>
     <row r="120" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="B120" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="C120">
         <v>724479261</v>
@@ -8456,7 +8326,7 @@
         <v>28463770</v>
       </c>
       <c r="E120" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="F120">
         <v>728649729</v>
@@ -8495,7 +8365,7 @@
         <v>24</v>
       </c>
       <c r="R120" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S120" t="s">
         <v>88</v>
@@ -8503,10 +8373,10 @@
     </row>
     <row r="121" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="B121" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C121">
         <v>713101470</v>
@@ -8515,7 +8385,7 @@
         <v>20043507</v>
       </c>
       <c r="E121" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="F121">
         <v>110724989</v>
@@ -8554,7 +8424,7 @@
         <v>24</v>
       </c>
       <c r="R121" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S121" t="s">
         <v>30</v>
@@ -8562,10 +8432,10 @@
     </row>
     <row r="122" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="B122" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="C122">
         <v>711869409</v>
@@ -8574,7 +8444,7 @@
         <v>13132580</v>
       </c>
       <c r="E122" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="F122">
         <v>710686602</v>
@@ -8613,7 +8483,7 @@
         <v>24</v>
       </c>
       <c r="R122" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S122" t="s">
         <v>30</v>
@@ -8621,10 +8491,10 @@
     </row>
     <row r="123" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="B123" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="C123">
         <v>729828281</v>
@@ -8633,7 +8503,7 @@
         <v>24015096</v>
       </c>
       <c r="E123" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="F123">
         <v>713328411</v>
@@ -8672,7 +8542,7 @@
         <v>24</v>
       </c>
       <c r="R123" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S123" t="s">
         <v>30</v>
@@ -8680,10 +8550,10 @@
     </row>
     <row r="124" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="B124" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C124">
         <v>711227118</v>
@@ -8692,7 +8562,7 @@
         <v>27071216</v>
       </c>
       <c r="E124" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="F124">
         <v>724382862</v>
@@ -8731,7 +8601,7 @@
         <v>24</v>
       </c>
       <c r="R124" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S124" t="s">
         <v>81</v>
@@ -8739,10 +8609,10 @@
     </row>
     <row r="125" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="B125" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="C125">
         <v>729518016</v>
@@ -8751,7 +8621,7 @@
         <v>31331138</v>
       </c>
       <c r="E125" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="F125">
         <v>711063122</v>
@@ -8790,7 +8660,7 @@
         <v>24</v>
       </c>
       <c r="R125" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S125" t="s">
         <v>30</v>
@@ -8798,10 +8668,10 @@
     </row>
     <row r="126" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="B126" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="C126">
         <v>729144308</v>
@@ -8810,7 +8680,7 @@
         <v>23118891</v>
       </c>
       <c r="E126" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="F126">
         <v>700570661</v>
@@ -8849,7 +8719,7 @@
         <v>24</v>
       </c>
       <c r="R126" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S126" t="s">
         <v>30</v>
@@ -8857,10 +8727,10 @@
     </row>
     <row r="127" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="B127" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="C127">
         <v>768824476</v>
@@ -8869,7 +8739,7 @@
         <v>27008294</v>
       </c>
       <c r="E127" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F127">
         <v>768094794</v>
@@ -8908,7 +8778,7 @@
         <v>24</v>
       </c>
       <c r="R127" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S127" t="s">
         <v>30</v>
@@ -8916,10 +8786,10 @@
     </row>
     <row r="128" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="B128" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="C128">
         <v>724836941</v>
@@ -8928,7 +8798,7 @@
         <v>22843423</v>
       </c>
       <c r="E128" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="F128">
         <v>743320897</v>
@@ -8967,7 +8837,7 @@
         <v>24</v>
       </c>
       <c r="R128" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S128" t="s">
         <v>88</v>
@@ -8975,10 +8845,10 @@
     </row>
     <row r="129" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="B129" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="C129">
         <v>714359854</v>
@@ -8987,7 +8857,7 @@
         <v>13065475</v>
       </c>
       <c r="E129" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="F129">
         <v>715778506</v>
@@ -9026,7 +8896,7 @@
         <v>24</v>
       </c>
       <c r="R129" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S129" t="s">
         <v>81</v>
@@ -9034,10 +8904,10 @@
     </row>
     <row r="130" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="B130" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="C130">
         <v>711973607</v>
@@ -9046,7 +8916,7 @@
         <v>13844462</v>
       </c>
       <c r="E130" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="F130">
         <v>742103835</v>
@@ -9085,7 +8955,7 @@
         <v>24</v>
       </c>
       <c r="R130" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S130" t="s">
         <v>26</v>
@@ -9093,10 +8963,10 @@
     </row>
     <row r="131" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="B131" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C131">
         <v>723849109</v>
@@ -9105,7 +8975,7 @@
         <v>10877984</v>
       </c>
       <c r="E131" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="F131">
         <v>711237285</v>
@@ -9144,7 +9014,7 @@
         <v>24</v>
       </c>
       <c r="R131" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S131" t="s">
         <v>30</v>
@@ -9152,10 +9022,10 @@
     </row>
     <row r="132" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="B132" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="C132">
         <v>729823193</v>
@@ -9164,7 +9034,7 @@
         <v>25321156</v>
       </c>
       <c r="E132" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F132">
         <v>717722011</v>
@@ -9203,7 +9073,7 @@
         <v>24</v>
       </c>
       <c r="R132" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S132" t="s">
         <v>81</v>
@@ -9211,10 +9081,10 @@
     </row>
     <row r="133" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="B133" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="C133">
         <v>707029040</v>
@@ -9223,7 +9093,7 @@
         <v>25234394</v>
       </c>
       <c r="E133" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="F133">
         <v>707029040</v>
@@ -9262,7 +9132,7 @@
         <v>24</v>
       </c>
       <c r="R133" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S133" t="s">
         <v>99</v>
@@ -9270,10 +9140,10 @@
     </row>
     <row r="134" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="B134" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="C134">
         <v>726683825</v>
@@ -9282,7 +9152,7 @@
         <v>26757694</v>
       </c>
       <c r="E134" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="F134">
         <v>746194202</v>
@@ -9321,7 +9191,7 @@
         <v>24</v>
       </c>
       <c r="R134" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S134" t="s">
         <v>30</v>
@@ -9329,10 +9199,10 @@
     </row>
     <row r="135" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="B135" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="C135">
         <v>758091413</v>
@@ -9341,7 +9211,7 @@
         <v>36004000</v>
       </c>
       <c r="E135" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="F135">
         <v>759607572</v>
@@ -9380,7 +9250,7 @@
         <v>24</v>
       </c>
       <c r="R135" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S135" t="s">
         <v>88</v>
@@ -9388,10 +9258,10 @@
     </row>
     <row r="136" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="B136" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C136">
         <v>745464053</v>
@@ -9400,7 +9270,7 @@
         <v>34005439</v>
       </c>
       <c r="E136" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="F136">
         <v>792049791</v>
@@ -9439,7 +9309,7 @@
         <v>24</v>
       </c>
       <c r="R136" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S136" t="s">
         <v>30</v>
@@ -9447,10 +9317,10 @@
     </row>
     <row r="137" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="B137" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="C137">
         <v>115006398</v>
@@ -9459,7 +9329,7 @@
         <v>29484668</v>
       </c>
       <c r="E137" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="F137">
         <v>794894574</v>
@@ -9498,7 +9368,7 @@
         <v>24</v>
       </c>
       <c r="R137" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S137" t="s">
         <v>88</v>
@@ -9506,10 +9376,10 @@
     </row>
     <row r="138" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="B138" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C138">
         <v>794817796</v>
@@ -9518,7 +9388,7 @@
         <v>21424507</v>
       </c>
       <c r="E138" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="F138">
         <v>702282198</v>
@@ -9557,7 +9427,7 @@
         <v>24</v>
       </c>
       <c r="R138" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S138" t="s">
         <v>88</v>
@@ -9565,7 +9435,7 @@
     </row>
     <row r="139" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="B139" t="s">
         <v>92</v>
@@ -9577,7 +9447,7 @@
         <v>31021311</v>
       </c>
       <c r="E139" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="F139">
         <v>711346285</v>
@@ -9616,7 +9486,7 @@
         <v>24</v>
       </c>
       <c r="R139" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S139" t="s">
         <v>30</v>
@@ -9624,10 +9494,10 @@
     </row>
     <row r="140" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="B140" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C140">
         <v>721950008</v>
@@ -9636,7 +9506,7 @@
         <v>20220180</v>
       </c>
       <c r="E140" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="F140">
         <v>727258550</v>
@@ -9675,7 +9545,7 @@
         <v>24</v>
       </c>
       <c r="R140" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S140" t="s">
         <v>88</v>
@@ -9683,10 +9553,10 @@
     </row>
     <row r="141" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="B141" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C141">
         <v>791542906</v>
@@ -9695,7 +9565,7 @@
         <v>13219284</v>
       </c>
       <c r="E141" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="F141">
         <v>710467216</v>
@@ -9734,7 +9604,7 @@
         <v>24</v>
       </c>
       <c r="R141" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S141" t="s">
         <v>30</v>
@@ -9742,10 +9612,10 @@
     </row>
     <row r="142" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="B142" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="C142">
         <v>758849257</v>
@@ -9754,7 +9624,7 @@
         <v>31047277</v>
       </c>
       <c r="E142" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="F142">
         <v>748300019</v>
@@ -9793,7 +9663,7 @@
         <v>24</v>
       </c>
       <c r="R142" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S142" t="s">
         <v>88</v>
@@ -9801,10 +9671,10 @@
     </row>
     <row r="143" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="B143" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="C143">
         <v>716339627</v>
@@ -9813,7 +9683,7 @@
         <v>3919278</v>
       </c>
       <c r="E143" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="F143">
         <v>740182164</v>
@@ -9852,7 +9722,7 @@
         <v>24</v>
       </c>
       <c r="R143" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S143" t="s">
         <v>88</v>
@@ -9860,10 +9730,10 @@
     </row>
     <row r="144" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="B144" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="C144">
         <v>703832288</v>
@@ -9872,7 +9742,7 @@
         <v>34273373</v>
       </c>
       <c r="E144" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="F144">
         <v>725544551</v>
@@ -9911,7 +9781,7 @@
         <v>24</v>
       </c>
       <c r="R144" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S144" t="s">
         <v>30</v>
@@ -9919,16 +9789,16 @@
     </row>
     <row r="145" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="B145" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C145">
         <v>715024838</v>
       </c>
       <c r="E145" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="F145">
         <v>705729772</v>
@@ -9967,7 +9837,7 @@
         <v>24</v>
       </c>
       <c r="R145" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S145" t="s">
         <v>88</v>
@@ -9975,10 +9845,10 @@
     </row>
     <row r="146" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="B146" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="C146">
         <v>113811503</v>
@@ -9987,7 +9857,7 @@
         <v>38594534</v>
       </c>
       <c r="E146" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="F146">
         <v>705287823</v>
@@ -10026,7 +9896,7 @@
         <v>24</v>
       </c>
       <c r="R146" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S146" t="s">
         <v>88</v>
@@ -10034,10 +9904,10 @@
     </row>
     <row r="147" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="B147" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="C147">
         <v>791981144</v>
@@ -10046,7 +9916,7 @@
         <v>25262744</v>
       </c>
       <c r="E147" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="F147">
         <v>714584701</v>
@@ -10085,7 +9955,7 @@
         <v>24</v>
       </c>
       <c r="R147" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S147" t="s">
         <v>30</v>
@@ -10093,10 +9963,10 @@
     </row>
     <row r="148" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="B148" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="C148">
         <v>728290725</v>
@@ -10105,7 +9975,7 @@
         <v>29150143</v>
       </c>
       <c r="E148" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="F148">
         <v>714592685</v>
@@ -10144,7 +10014,7 @@
         <v>24</v>
       </c>
       <c r="R148" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S148" t="s">
         <v>69</v>
@@ -10152,10 +10022,10 @@
     </row>
     <row r="149" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="B149" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="C149">
         <v>743647697</v>
@@ -10164,7 +10034,7 @@
         <v>31385905</v>
       </c>
       <c r="E149" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="F149">
         <v>741796731</v>
@@ -10203,7 +10073,7 @@
         <v>24</v>
       </c>
       <c r="R149" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S149" t="s">
         <v>88</v>
@@ -10211,10 +10081,10 @@
     </row>
     <row r="150" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="B150" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="C150">
         <v>700677627</v>
@@ -10223,7 +10093,7 @@
         <v>37384637</v>
       </c>
       <c r="E150" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="F150">
         <v>724348241</v>
@@ -10262,7 +10132,7 @@
         <v>24</v>
       </c>
       <c r="R150" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S150" t="s">
         <v>30</v>
@@ -10270,10 +10140,10 @@
     </row>
     <row r="151" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="B151" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="C151">
         <v>748485559</v>
@@ -10282,7 +10152,7 @@
         <v>28086482</v>
       </c>
       <c r="E151" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="F151">
         <v>791470552</v>
@@ -10321,7 +10191,7 @@
         <v>24</v>
       </c>
       <c r="R151" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S151" t="s">
         <v>30</v>
@@ -10329,10 +10199,10 @@
     </row>
     <row r="152" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="B152" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="C152">
         <v>798632927</v>
@@ -10341,7 +10211,7 @@
         <v>28111307</v>
       </c>
       <c r="E152" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="F152">
         <v>720323599</v>
@@ -10380,7 +10250,7 @@
         <v>24</v>
       </c>
       <c r="R152" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S152" t="s">
         <v>88</v>
@@ -10388,10 +10258,10 @@
     </row>
     <row r="153" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="B153" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="C153">
         <v>722527858</v>
@@ -10400,7 +10270,7 @@
         <v>8443023</v>
       </c>
       <c r="E153" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="F153">
         <v>722706813</v>
@@ -10439,7 +10309,7 @@
         <v>24</v>
       </c>
       <c r="R153" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S153" t="s">
         <v>30</v>
@@ -10447,10 +10317,10 @@
     </row>
     <row r="154" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="B154" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="C154">
         <v>720241837</v>
@@ -10459,7 +10329,7 @@
         <v>23912762</v>
       </c>
       <c r="E154" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="F154">
         <v>794326731</v>
@@ -10498,7 +10368,7 @@
         <v>24</v>
       </c>
       <c r="R154" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S154" t="s">
         <v>88</v>
@@ -10506,10 +10376,10 @@
     </row>
     <row r="155" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="B155" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="C155">
         <v>720630896</v>
@@ -10518,7 +10388,7 @@
         <v>2219045</v>
       </c>
       <c r="E155" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="F155">
         <v>113244500</v>
@@ -10557,7 +10427,7 @@
         <v>24</v>
       </c>
       <c r="R155" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S155" t="s">
         <v>30</v>
@@ -10565,10 +10435,10 @@
     </row>
     <row r="156" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="B156" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="C156">
         <v>722655548</v>
@@ -10577,7 +10447,7 @@
         <v>6828057</v>
       </c>
       <c r="E156" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="F156">
         <v>701481316</v>
@@ -10616,7 +10486,7 @@
         <v>24</v>
       </c>
       <c r="R156" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S156" t="s">
         <v>30</v>
@@ -10624,10 +10494,10 @@
     </row>
     <row r="157" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="B157" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="C157">
         <v>704163771</v>
@@ -10636,7 +10506,7 @@
         <v>22008964</v>
       </c>
       <c r="E157" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="F157">
         <v>727306592</v>
@@ -10675,7 +10545,7 @@
         <v>24</v>
       </c>
       <c r="R157" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S157" t="s">
         <v>26</v>
@@ -10683,10 +10553,10 @@
     </row>
     <row r="158" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="B158" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="C158">
         <v>714503794</v>
@@ -10695,7 +10565,7 @@
         <v>22285121</v>
       </c>
       <c r="E158" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="F158">
         <v>745128614</v>
@@ -10734,7 +10604,7 @@
         <v>24</v>
       </c>
       <c r="R158" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S158" t="s">
         <v>30</v>
@@ -10742,10 +10612,10 @@
     </row>
     <row r="159" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="B159" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="C159">
         <v>717622386</v>
@@ -10754,7 +10624,7 @@
         <v>12949818</v>
       </c>
       <c r="E159" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="F159">
         <v>1088117449</v>
@@ -10793,7 +10663,7 @@
         <v>24</v>
       </c>
       <c r="R159" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S159" t="s">
         <v>112</v>
@@ -10801,10 +10671,10 @@
     </row>
     <row r="160" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="B160" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="C160">
         <v>726949202</v>
@@ -10813,7 +10683,7 @@
         <v>10810897</v>
       </c>
       <c r="E160" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="F160">
         <v>728773170</v>
@@ -10852,7 +10722,7 @@
         <v>24</v>
       </c>
       <c r="R160" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S160" t="s">
         <v>88</v>
@@ -10860,10 +10730,10 @@
     </row>
     <row r="161" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="B161" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="C161">
         <v>742033906</v>
@@ -10911,7 +10781,7 @@
         <v>24</v>
       </c>
       <c r="R161" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S161" t="s">
         <v>30</v>
@@ -10919,10 +10789,10 @@
     </row>
     <row r="162" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="B162" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="C162">
         <v>701035799</v>
@@ -10931,7 +10801,7 @@
         <v>2308800</v>
       </c>
       <c r="E162" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="F162">
         <v>703322932</v>
@@ -10970,7 +10840,7 @@
         <v>24</v>
       </c>
       <c r="R162" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="S162" t="s">
         <v>69</v>
